--- a/项目搜索关键词整理.xlsx
+++ b/项目搜索关键词整理.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZY\Desktop\SemiCrawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E6C8AB48-C797-42A9-8380-72CAF07AF65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D42870-B4E5-47ED-BC63-723DE6954101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2052" yWindow="3948" windowWidth="23040" windowHeight="12204" activeTab="2" xr2:uid="{B871AB74-23FB-45DE-8DC2-0D70C9D593FC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{B871AB74-23FB-45DE-8DC2-0D70C9D593FC}"/>
   </bookViews>
   <sheets>
     <sheet name="技术名词" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="95">
   <si>
     <t>二级行业</t>
   </si>
@@ -298,6 +298,18 @@
   </si>
   <si>
     <t>签约、落户、落地、新建、扩建、扩产、建设、揭牌、流片、规划、投资、长期协议、战略合作、项目立项</t>
+  </si>
+  <si>
+    <t>集成电路</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>芯片</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>半导体</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1269,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3FF8191-6CBE-4A0D-B28C-0B200094A9FE}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1634,6 +1646,21 @@
       </c>
       <c r="C44" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
